--- a/artfynd/A 7959-2022 artfynd.xlsx
+++ b/artfynd/A 7959-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7959-2022 artfynd.xlsx
+++ b/artfynd/A 7959-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112026849</v>
+        <v>112026980</v>
       </c>
       <c r="B2" t="n">
-        <v>90858</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5448</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>817551</v>
+        <v>817395</v>
       </c>
       <c r="R2" t="n">
-        <v>7526465</v>
+        <v>7526085</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,12 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112026951</v>
+        <v>112026965</v>
       </c>
       <c r="B3" t="n">
-        <v>90801</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3100</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>817535</v>
+        <v>817590</v>
       </c>
       <c r="R3" t="n">
-        <v>7526456</v>
+        <v>7526115</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112026980</v>
+        <v>112026800</v>
       </c>
       <c r="B4" t="n">
-        <v>77732</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,27 +896,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -942,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>817396</v>
+        <v>817625</v>
       </c>
       <c r="R4" t="n">
-        <v>7526085</v>
+        <v>7526475</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,6 +987,951 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112026951</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93222</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>817535</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7526455</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112026795</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>817625</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7526475</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112026808</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>817625</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7526470</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112026821</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>817619</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7526470</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112026829</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>817615</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7526470</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112026805</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>817625</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7526470</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112026849</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>817550</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7526465</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112026748</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>817645</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7526470</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112026975</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>817580</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7526130</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7959-2022 artfynd.xlsx
+++ b/artfynd/A 7959-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026980</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026965</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026800</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026951</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026795</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026808</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026821</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026829</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026805</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026849</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026748</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1932,8 +1992,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026975</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>